--- a/artfynd/A 56700-2025 artfynd.xlsx
+++ b/artfynd/A 56700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,45 +1025,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132540298</v>
+        <v>137538831</v>
       </c>
       <c r="B5" t="n">
-        <v>57386</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>100136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla, Sm</t>
+          <t>Kindbäcksmåla lappuggla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545757</v>
+        <v>545627</v>
       </c>
       <c r="R5" t="n">
-        <v>6263812</v>
+        <v>6263817</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,22 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,33 +1133,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132540298</t>
+          <t>https://artportalen.se/Sighting/137538831</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132441624</v>
+        <v>132540298</v>
       </c>
       <c r="B6" t="n">
-        <v>58349</v>
+        <v>57386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1202,22 +1204,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,13 +1245,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132441624</t>
+          <t>https://artportalen.se/Sighting/132540298</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132443241</v>
+        <v>132441624</v>
       </c>
       <c r="B7" t="n">
         <v>58349</v>
@@ -1280,14 +1282,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla.1, Sm</t>
+          <t>Kindbäcksmåla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545607</v>
+        <v>545757</v>
       </c>
       <c r="R7" t="n">
-        <v>6263714</v>
+        <v>6263812</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,64 +1357,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132443241</t>
+          <t>https://artportalen.se/Sighting/132441624</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132876666</v>
+        <v>132443241</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla.1 talltitan, Sm</t>
+          <t>Kindbäcksmåla.1, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545583</v>
+        <v>545607</v>
       </c>
       <c r="R8" t="n">
-        <v>6263727</v>
+        <v>6263714</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,12 +1428,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,6 +1468,118 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132443241</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132876666</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kindbäcksmåla.1 talltitan, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>545583</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6263727</v>
+      </c>
+      <c r="S9" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132876666</t>
         </is>
@@ -1480,6 +1594,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
